--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:59</t>
+    <t xml:space="preserve">2026-08-05 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:56</t>
+    <t xml:space="preserve">2026-08-16 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:04</t>
+    <t xml:space="preserve">2026-08-19 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:25</t>
+    <t xml:space="preserve">2026-08-28 12:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:12</t>
+    <t xml:space="preserve">2026-09-06 17:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
